--- a/layout/LayoutTenencia_V2_FT_TENENCIA.xlsx
+++ b/layout/LayoutTenencia_V2_FT_TENENCIA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\LOCAL\DESA\non-purple-wheel\non-purple-wheel\layout\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2627D65B-17F8-4117-98AE-4D912DDD8708}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E4D46E4-DFDD-434D-A80E-8C72D7F7636C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3000" yWindow="1200" windowWidth="21600" windowHeight="11310" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FT_TENENCIA" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="55">
   <si>
     <t>Descripcion</t>
   </si>
@@ -63,9 +63,6 @@
   </si>
   <si>
     <t>Opcional Reportes</t>
-  </si>
-  <si>
-    <t>Comentario BW</t>
   </si>
   <si>
     <t>TITULOOBJETO</t>
@@ -114,9 +111,6 @@
   </si>
   <si>
     <t>CASFIM</t>
-  </si>
-  <si>
-    <t>CONTRAPARTES</t>
   </si>
   <si>
     <t>MONEDA</t>
@@ -336,25 +330,7 @@
     <cellStyle name="Normal 2 3 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
     <cellStyle name="Normal 3" xfId="2" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
   </cellStyles>
-  <dxfs count="11">
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <bgColor auto="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="10">
     <dxf>
       <font>
         <strike val="0"/>
@@ -556,19 +532,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table2457109104" displayName="Table2457109104" ref="A1:K12" totalsRowShown="0" dataDxfId="10">
-  <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Orden" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Nombre" dataDxfId="8"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Tipo" dataDxfId="7"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table2457109104" displayName="Table2457109104" ref="A1:J12" totalsRowShown="0" dataDxfId="9">
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Orden" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Nombre" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Tipo" dataDxfId="6"/>
     <tableColumn id="10" xr3:uid="{961D497B-8BC3-4921-850B-BDB5EED0AA7D}" name="Formato"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Uso" dataDxfId="6"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Descripcion" dataDxfId="5"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Validacion" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Catalogo" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{900224BE-0F26-41E2-925E-2BCC37A8EFB9}" name="Requerido Reportes" dataDxfId="2" dataCellStyle="Normal 3"/>
-    <tableColumn id="6" xr3:uid="{8C3ADAC6-5441-4E14-A26D-AF3CB2A904E9}" name="Opcional Reportes" dataDxfId="1"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Comentario BW" dataDxfId="0"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Uso" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Descripcion" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Validacion" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Catalogo" dataDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{900224BE-0F26-41E2-925E-2BCC37A8EFB9}" name="Requerido Reportes" dataDxfId="1" dataCellStyle="Normal 3"/>
+    <tableColumn id="6" xr3:uid="{8C3ADAC6-5441-4E14-A26D-AF3CB2A904E9}" name="Opcional Reportes" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -840,30 +815,29 @@
   <sheetPr>
     <tabColor theme="6" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:L20"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:K20"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.77734375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.6640625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="17.44140625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="41.109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="17.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="23.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="29.88671875" style="1" customWidth="1"/>
-    <col min="12" max="12" width="27.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="14.6640625" style="1" customWidth="1"/>
-    <col min="16" max="16" width="9.109375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="15.6640625" style="1" customWidth="1"/>
-    <col min="18" max="18" width="9.109375" style="1"/>
-    <col min="19" max="19" width="28.88671875" style="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.109375" style="1"/>
+    <col min="1" max="1" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.85546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="17.42578125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="62.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="27.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="14" width="14.5703125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="9.140625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="15.5703125" style="1" customWidth="1"/>
+    <col min="17" max="17" width="9.140625" style="1"/>
+    <col min="18" max="18" width="28.85546875" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -874,7 +848,7 @@
         <v>4</v>
       </c>
       <c r="D1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E1" t="s">
         <v>1</v>
@@ -894,393 +868,361 @@
       <c r="J1" t="s">
         <v>8</v>
       </c>
-      <c r="K1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1"/>
-    </row>
-    <row r="2" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="K1"/>
+    </row>
+    <row r="2" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D2" s="3">
         <v>18</v>
       </c>
       <c r="E2" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" t="s">
         <v>12</v>
-      </c>
-      <c r="G2" t="s">
-        <v>13</v>
       </c>
       <c r="H2"/>
       <c r="I2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J2" t="s">
         <v>14</v>
       </c>
-      <c r="J2" t="s">
-        <v>15</v>
-      </c>
-      <c r="K2" t="s">
-        <v>10</v>
-      </c>
-      <c r="L2"/>
-    </row>
-    <row r="3" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="K2"/>
+    </row>
+    <row r="3" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D3">
         <v>12</v>
       </c>
       <c r="E3" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" t="s">
         <v>17</v>
-      </c>
-      <c r="G3" t="s">
-        <v>18</v>
       </c>
       <c r="H3"/>
       <c r="I3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" t="s">
         <v>14</v>
       </c>
-      <c r="J3" t="s">
-        <v>15</v>
-      </c>
-      <c r="K3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L3"/>
-    </row>
-    <row r="4" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="K3"/>
+    </row>
+    <row r="4" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D4">
         <v>6</v>
       </c>
       <c r="E4" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G4" t="s">
         <v>21</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>22</v>
       </c>
-      <c r="H4" t="s">
-        <v>23</v>
-      </c>
       <c r="I4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J4" t="s">
         <v>14</v>
       </c>
-      <c r="J4" t="s">
-        <v>15</v>
-      </c>
-      <c r="K4" t="s">
-        <v>24</v>
-      </c>
-      <c r="L4"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="K4"/>
+    </row>
+    <row r="5" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D5">
         <v>3</v>
       </c>
       <c r="E5" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G5" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="H5" t="s">
         <v>27</v>
       </c>
-      <c r="G5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H5" t="s">
-        <v>29</v>
-      </c>
       <c r="I5" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J5" t="s">
-        <v>14</v>
-      </c>
-      <c r="K5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L5"/>
-    </row>
-    <row r="6" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+      <c r="K5"/>
+    </row>
+    <row r="6" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" t="s">
+        <v>51</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" t="s">
         <v>30</v>
-      </c>
-      <c r="C6" t="s">
-        <v>56</v>
-      </c>
-      <c r="D6" t="s">
-        <v>53</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="G6" t="s">
-        <v>32</v>
       </c>
       <c r="H6"/>
       <c r="I6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J6" t="s">
         <v>14</v>
       </c>
-      <c r="J6" t="s">
-        <v>15</v>
-      </c>
-      <c r="K6" t="s">
-        <v>30</v>
-      </c>
-      <c r="L6"/>
-    </row>
-    <row r="7" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="K6"/>
+    </row>
+    <row r="7" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H7"/>
       <c r="I7" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J7" t="s">
         <v>14</v>
       </c>
-      <c r="J7" t="s">
-        <v>15</v>
-      </c>
-      <c r="K7" t="s">
-        <v>33</v>
-      </c>
-      <c r="L7"/>
-    </row>
-    <row r="8" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="K7"/>
+    </row>
+    <row r="8" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D8">
         <v>2</v>
       </c>
       <c r="E8" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H8" t="s">
         <v>36</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G8" t="s">
-        <v>22</v>
-      </c>
-      <c r="H8" t="s">
-        <v>38</v>
-      </c>
       <c r="I8" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J8" t="s">
         <v>14</v>
       </c>
-      <c r="J8" t="s">
-        <v>15</v>
-      </c>
-      <c r="K8" t="s">
-        <v>35</v>
-      </c>
-      <c r="L8"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="K8"/>
+    </row>
+    <row r="9" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C9" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
       <c r="E9" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G9" t="s">
+        <v>21</v>
+      </c>
+      <c r="H9" t="s">
         <v>40</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G9" t="s">
-        <v>22</v>
-      </c>
-      <c r="H9" t="s">
-        <v>42</v>
-      </c>
       <c r="I9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J9" t="s">
         <v>14</v>
       </c>
-      <c r="J9" t="s">
-        <v>15</v>
-      </c>
-      <c r="K9" t="s">
-        <v>39</v>
-      </c>
-      <c r="L9"/>
-    </row>
-    <row r="10" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="K9"/>
+    </row>
+    <row r="10" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C10" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D10">
         <v>10</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H10" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I10" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J10" t="s">
         <v>14</v>
       </c>
-      <c r="J10" t="s">
-        <v>15</v>
-      </c>
-      <c r="K10" t="s">
-        <v>43</v>
-      </c>
-      <c r="L10"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="K10"/>
+    </row>
+    <row r="11" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D11" s="8">
         <v>1</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I11" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J11" t="s">
         <v>14</v>
       </c>
-      <c r="J11" t="s">
-        <v>15</v>
-      </c>
       <c r="K11"/>
-      <c r="L11"/>
-    </row>
-    <row r="12" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D12" s="8">
         <v>1</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H12" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="I12" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J12" t="s">
         <v>14</v>
       </c>
-      <c r="J12" t="s">
-        <v>15</v>
-      </c>
       <c r="K12"/>
-      <c r="L12"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B13"/>
       <c r="C13"/>
       <c r="D13"/>
@@ -1291,9 +1233,8 @@
       <c r="I13"/>
       <c r="J13"/>
       <c r="K13"/>
-      <c r="L13"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B14"/>
       <c r="C14"/>
       <c r="D14"/>
@@ -1304,9 +1245,8 @@
       <c r="I14"/>
       <c r="J14"/>
       <c r="K14"/>
-      <c r="L14"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B15"/>
       <c r="C15"/>
       <c r="D15"/>
@@ -1317,9 +1257,8 @@
       <c r="I15"/>
       <c r="J15"/>
       <c r="K15"/>
-      <c r="L15"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B16"/>
       <c r="C16"/>
       <c r="D16"/>
@@ -1329,9 +1268,8 @@
       <c r="H16"/>
       <c r="I16"/>
       <c r="J16"/>
-      <c r="K16"/>
-    </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17"/>
       <c r="C17"/>
       <c r="D17"/>
@@ -1341,9 +1279,8 @@
       <c r="H17"/>
       <c r="I17"/>
       <c r="J17"/>
-      <c r="K17"/>
-    </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18"/>
       <c r="C18"/>
       <c r="D18"/>
@@ -1353,9 +1290,8 @@
       <c r="H18"/>
       <c r="I18"/>
       <c r="J18"/>
-      <c r="K18"/>
-    </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19"/>
       <c r="C19"/>
       <c r="D19"/>
@@ -1365,9 +1301,8 @@
       <c r="H19"/>
       <c r="I19"/>
       <c r="J19"/>
-      <c r="K19"/>
-    </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20"/>
       <c r="C20"/>
       <c r="D20"/>
@@ -1377,7 +1312,6 @@
       <c r="H20"/>
       <c r="I20"/>
       <c r="J20"/>
-      <c r="K20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
